--- a/pre_survey_responses.xlsx
+++ b/pre_survey_responses.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,13 +609,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>None</t>
@@ -626,6 +624,147 @@
       </c>
       <c r="L4" t="n">
         <v>2.03</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>band4life</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Violin, 2 years in high school</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4.02</v>
       </c>
     </row>
   </sheetData>

--- a/pre_survey_responses.xlsx
+++ b/pre_survey_responses.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,13 +748,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Violin, 2 years in high school</t>
@@ -765,6 +763,56 @@
       </c>
       <c r="L7" t="n">
         <v>4.02</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>French Horn, 3 years in middle school. Hand Percussion, 3 years in high school.</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7.07</v>
       </c>
     </row>
   </sheetData>
